--- a/Tools/Luban/DataTables/Datas/CozyYard/animal.xlsx
+++ b/Tools/Luban/DataTables/Datas/CozyYard/animal.xlsx
@@ -30,7 +30,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,9 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -432,11 +441,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -496,109 +505,156 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##type</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>名称</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>类型(Poultry/Aquatic/Pet)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>产出物品ID</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>产出周期(天)</t>
+          <t>int</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>需要设施ID</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>饲料物品ID</t>
+          <t>int</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>每次喂食量</t>
+          <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>鸡</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Poultry</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>3101</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>类型(Poultry/Aquatic/Pet)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>产出物品ID</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>产出周期(天)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>需要设施ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>饲料物品ID</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>每次喂食量</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>鸡</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Poultry</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3101</v>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>猫</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Pet</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
